--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -1,121 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6491AD-D283-1A4A-A76E-C15578EBB1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="organizations" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="organizations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">organizations!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$W$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>slug</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>legal_status</t>
-  </si>
-  <si>
-    <t>ownership</t>
-  </si>
-  <si>
-    <t>mission</t>
-  </si>
-  <si>
-    <t>known_for</t>
-  </si>
-  <si>
-    <t>activities</t>
-  </si>
-  <si>
-    <t>project</t>
-  </si>
-  <si>
-    <t>research_areas</t>
-  </si>
-  <si>
-    <t>products</t>
-  </si>
-  <si>
-    <t>services</t>
-  </si>
-  <si>
-    <t>partnerships</t>
-  </si>
-  <si>
-    <t>budget</t>
-  </si>
-  <si>
-    <t>founded</t>
-  </si>
-  <si>
-    <t>founder</t>
-  </si>
-  <si>
-    <t>equipments</t>
-  </si>
-  <si>
-    <t>score</t>
-  </si>
-  <si>
-    <t>city_id</t>
-  </si>
-  <si>
-    <t>numberOfEmployees</t>
-  </si>
-  <si>
-    <t>numberOfSubsidiaries</t>
-  </si>
-  <si>
-    <t>parent_organization_id</t>
-  </si>
-  <si>
-    <t>metadata</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -139,23 +59,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -443,95 +422,213 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="21" customWidth="1"/>
-    <col min="21" max="21" width="24" customWidth="1"/>
-    <col min="22" max="22" width="26" customWidth="1"/>
-    <col min="23" max="23" width="18" customWidth="1"/>
+    <col width="18" customWidth="1" min="1" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>legal_status</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>ownership</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>mission</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>known_for</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>activities</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>research_areas</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>products</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>partnerships</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>founded</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>founder</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>equipments</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>city_id</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>numberOfEmployees</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>numberOfSubsidiaries</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>parent_organization_id</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8kSec</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8ksec</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACI Financial Markets Association</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aci-financial-markets-association</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOCIETY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>adobe</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Adobe (Magento)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>adobe-magento</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:W1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C999" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="C2:C999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"COMPANY,GOVERNMENT,RESEARCH_INSTITUTE,UNIVERSITY,INTERNATIONAL_ORGANIZATION,NGO,NON_PROFIT,SOCIETY,CLUB,ARMY,OTHER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T2:T999" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation sqref="T2:T999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"RANGE_1_10,RANGE_11_50,RANGE_51_200,RANGE_201_1000,RANGE_1001_5000,RANGE_5000_PLUS"</formula1>
     </dataValidation>
   </dataValidations>

--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -1,41 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel_templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB59853-3078-2D4B-815C-BCB3903B00B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="organizations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="organizations" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">organizations!$A$1:$X$1</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>slug</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>legal_status</t>
+  </si>
+  <si>
+    <t>ownership</t>
+  </si>
+  <si>
+    <t>mission</t>
+  </si>
+  <si>
+    <t>known_for</t>
+  </si>
+  <si>
+    <t>activities</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>research_areas</t>
+  </si>
+  <si>
+    <t>products</t>
+  </si>
+  <si>
+    <t>services</t>
+  </si>
+  <si>
+    <t>partnerships</t>
+  </si>
+  <si>
+    <t>budget</t>
+  </si>
+  <si>
+    <t>founded</t>
+  </si>
+  <si>
+    <t>founder</t>
+  </si>
+  <si>
+    <t>equipments</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>city_id</t>
+  </si>
+  <si>
+    <t>numberOfEmployees</t>
+  </si>
+  <si>
+    <t>numberOfSubsidiaries</t>
+  </si>
+  <si>
+    <t>parent_organization_id</t>
+  </si>
+  <si>
+    <t>metadata</t>
+  </si>
+  <si>
+    <t>8kSec</t>
+  </si>
+  <si>
+    <t>8ksec</t>
+  </si>
+  <si>
+    <t>COMPANY</t>
+  </si>
+  <si>
+    <t>ACI Financial Markets Association</t>
+  </si>
+  <si>
+    <t>aci-financial-markets-association</t>
+  </si>
+  <si>
+    <t>SOCIETY</t>
+  </si>
+  <si>
+    <t>Adobe</t>
+  </si>
+  <si>
+    <t>adobe</t>
+  </si>
+  <si>
+    <t>Adobe (Magento)</t>
+  </si>
+  <si>
+    <t>adobe-magento</t>
+  </si>
+  <si>
+    <t>subtype</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -59,82 +172,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -422,216 +476,148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="26" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="21" customWidth="1"/>
+    <col min="22" max="22" width="24" customWidth="1"/>
+    <col min="23" max="23" width="26" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>legal_status</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>ownership</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>mission</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>known_for</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>project</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>research_areas</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>products</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>services</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>partnerships</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>budget</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>founded</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>founder</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>equipments</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>city_id</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>numberOfEmployees</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>numberOfSubsidiaries</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>parent_organization_id</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>metadata</t>
-        </is>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>8kSec</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>8ksec</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>COMPANY</t>
-        </is>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ACI Financial Markets Association</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>aci-financial-markets-association</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SOCIETY</t>
-        </is>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>adobe</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>COMPANY</t>
-        </is>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Adobe (Magento)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>adobe-magento</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>COMPANY</t>
-        </is>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:X1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="U2:U999" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"RANGE_1_10,RANGE_11_50,RANGE_51_200,RANGE_201_1000,RANGE_1001_5000,RANGE_5000_PLUS"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C6:D999 C2:C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"COMPANY,GOVERNMENT,RESEARCH_INSTITUTE,UNIVERSITY,INTERNATIONAL_ORGANIZATION,NGO,NON_PROFIT,SOCIETY,CLUB,ARMY,OTHER"</formula1>
-    </dataValidation>
-    <dataValidation sqref="T2:T999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"RANGE_1_10,RANGE_11_50,RANGE_51_200,RANGE_201_1000,RANGE_1001_5000,RANGE_5000_PLUS"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -1,161 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel_templates/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB59853-3078-2D4B-815C-BCB3903B00B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="organizations" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="organizations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">organizations!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$Y$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>slug</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>legal_status</t>
-  </si>
-  <si>
-    <t>ownership</t>
-  </si>
-  <si>
-    <t>mission</t>
-  </si>
-  <si>
-    <t>known_for</t>
-  </si>
-  <si>
-    <t>activities</t>
-  </si>
-  <si>
-    <t>project</t>
-  </si>
-  <si>
-    <t>research_areas</t>
-  </si>
-  <si>
-    <t>products</t>
-  </si>
-  <si>
-    <t>services</t>
-  </si>
-  <si>
-    <t>partnerships</t>
-  </si>
-  <si>
-    <t>budget</t>
-  </si>
-  <si>
-    <t>founded</t>
-  </si>
-  <si>
-    <t>founder</t>
-  </si>
-  <si>
-    <t>equipments</t>
-  </si>
-  <si>
-    <t>score</t>
-  </si>
-  <si>
-    <t>city_id</t>
-  </si>
-  <si>
-    <t>numberOfEmployees</t>
-  </si>
-  <si>
-    <t>numberOfSubsidiaries</t>
-  </si>
-  <si>
-    <t>parent_organization_id</t>
-  </si>
-  <si>
-    <t>metadata</t>
-  </si>
-  <si>
-    <t>8kSec</t>
-  </si>
-  <si>
-    <t>8ksec</t>
-  </si>
-  <si>
-    <t>COMPANY</t>
-  </si>
-  <si>
-    <t>ACI Financial Markets Association</t>
-  </si>
-  <si>
-    <t>aci-financial-markets-association</t>
-  </si>
-  <si>
-    <t>SOCIETY</t>
-  </si>
-  <si>
-    <t>Adobe</t>
-  </si>
-  <si>
-    <t>adobe</t>
-  </si>
-  <si>
-    <t>Adobe (Magento)</t>
-  </si>
-  <si>
-    <t>adobe-magento</t>
-  </si>
-  <si>
-    <t>subtype</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,24 +56,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -476,148 +422,178 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="21" customWidth="1"/>
-    <col min="22" max="22" width="24" customWidth="1"/>
-    <col min="23" max="23" width="26" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="2" max="2"/>
+    <col width="18" customWidth="1" style="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="1" min="4" max="4"/>
+    <col width="18" customWidth="1" style="1" min="5" max="5"/>
+    <col width="18" customWidth="1" style="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="1" min="7" max="7"/>
+    <col width="18" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18" customWidth="1" style="1" min="9" max="9"/>
+    <col width="18" customWidth="1" style="1" min="10" max="10"/>
+    <col width="18" customWidth="1" style="1" min="11" max="11"/>
+    <col width="18" customWidth="1" style="1" min="12" max="12"/>
+    <col width="18" customWidth="1" style="1" min="13" max="13"/>
+    <col width="18" customWidth="1" style="1" min="14" max="14"/>
+    <col width="18" customWidth="1" style="1" min="15" max="15"/>
+    <col width="18" customWidth="1" style="1" min="16" max="16"/>
+    <col width="18" customWidth="1" style="1" min="17" max="17"/>
+    <col width="18" customWidth="1" style="1" min="18" max="18"/>
+    <col width="18" customWidth="1" style="2" min="19" max="19"/>
+    <col width="18" customWidth="1" style="1" min="20" max="20"/>
+    <col width="21" customWidth="1" style="1" min="21" max="21"/>
+    <col width="18" customWidth="1" style="2" min="22" max="22"/>
+    <col width="24" customWidth="1" style="2" min="23" max="23"/>
+    <col width="26" customWidth="1" style="1" min="24" max="24"/>
+    <col width="18" customWidth="1" style="1" min="25" max="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>subtype</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>legal_status</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>ownership</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>mission</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>known_for</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>activities</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>research_areas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>products</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>partnerships</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>founded</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>founder</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>equipments</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>city_id</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>numberOfEmployees</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>personnel</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>numberOfSubsidiaries</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>parent_organization_id</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Y1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="U2:U999" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"COMPANY,GOVERNMENT,RESEARCH_INSTITUTE,UNIVERSITY,INTERNATIONAL_ORGANIZATION,NGO,NON_PROFIT,SOCIETY,CLUB,ARMY,OTHER"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"RANGE_1_10,RANGE_11_50,RANGE_51_200,RANGE_201_1000,RANGE_1001_5000,RANGE_5000_PLUS"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C6:D999 C2:C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"COMPANY,GOVERNMENT,RESEARCH_INSTITUTE,UNIVERSITY,INTERNATIONAL_ORGANIZATION,NGO,NON_PROFIT,SOCIETY,CLUB,ARMY,OTHER"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -592,7 +592,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:Y1"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="2" state="veryHidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$Y$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$AE$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,18 +57,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,34 +432,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="5" min="1" max="1"/>
-    <col width="18" customWidth="1" style="5" min="2" max="2"/>
-    <col width="18" customWidth="1" style="5" min="3" max="3"/>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="2" max="2"/>
+    <col width="18" customWidth="1" style="1" min="3" max="3"/>
     <col width="18" customWidth="1" style="1" min="4" max="4"/>
     <col width="18" customWidth="1" style="1" min="5" max="5"/>
-    <col width="18" customWidth="1" style="5" min="6" max="6"/>
-    <col width="18" customWidth="1" style="5" min="7" max="7"/>
-    <col width="18" customWidth="1" style="5" min="8" max="8"/>
-    <col width="18" customWidth="1" style="1" min="9" max="9"/>
-    <col width="18" customWidth="1" style="5" min="10" max="10"/>
-    <col width="18" customWidth="1" style="5" min="11" max="11"/>
-    <col width="18" customWidth="1" style="5" min="12" max="12"/>
-    <col width="18" customWidth="1" style="5" min="13" max="13"/>
+    <col width="18" customWidth="1" style="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="1" min="7" max="7"/>
+    <col width="18" customWidth="1" style="1" min="8" max="8"/>
+    <col width="23" customWidth="1" style="1" min="9" max="9"/>
+    <col width="18" customWidth="1" style="1" min="10" max="10"/>
+    <col width="18" customWidth="1" style="1" min="11" max="11"/>
+    <col width="18" customWidth="1" style="1" min="12" max="12"/>
+    <col width="18" customWidth="1" style="1" min="13" max="13"/>
     <col width="18" customWidth="1" style="1" min="14" max="14"/>
-    <col width="18" customWidth="1" style="5" min="15" max="15"/>
-    <col width="18" customWidth="1" style="5" min="16" max="16"/>
+    <col width="18" customWidth="1" style="1" min="15" max="15"/>
+    <col width="18" customWidth="1" style="1" min="16" max="16"/>
     <col width="18" customWidth="1" style="1" min="17" max="17"/>
     <col width="18" customWidth="1" style="1" min="18" max="18"/>
-    <col width="18" customWidth="1" style="6" min="19" max="19"/>
-    <col width="18" customWidth="1" style="5" min="20" max="20"/>
-    <col width="21" customWidth="1" style="5" min="21" max="21"/>
-    <col width="18" customWidth="1" style="6" min="22" max="22"/>
-    <col width="24" customWidth="1" style="6" min="23" max="23"/>
-    <col width="26" customWidth="1" style="5" min="24" max="24"/>
-    <col width="18" customWidth="1" style="5" min="25" max="25"/>
+    <col width="18" customWidth="1" style="1" min="19" max="19"/>
+    <col width="18" customWidth="1" style="1" min="20" max="20"/>
+    <col width="18" customWidth="1" style="2" min="21" max="21"/>
+    <col width="18" customWidth="1" style="1" min="22" max="22"/>
+    <col width="18" customWidth="1" style="1" min="23" max="23"/>
+    <col width="18" customWidth="1" style="1" min="24" max="24"/>
+    <col width="18" customWidth="1" style="2" min="25" max="25"/>
+    <col width="18" customWidth="1" style="1" min="26" max="26"/>
+    <col width="21" customWidth="1" style="1" min="27" max="27"/>
+    <col width="18" customWidth="1" style="2" min="28" max="28"/>
+    <col width="24" customWidth="1" style="2" min="29" max="29"/>
+    <col width="26" customWidth="1" style="1" min="30" max="30"/>
+    <col width="18" customWidth="1" style="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,12 +486,12 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>type1</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>legal_status</t>
+          <t>type2</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
@@ -507,7 +511,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>activities</t>
+          <t>programs_activities</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
@@ -532,7 +536,7 @@
       </c>
       <c r="N1" s="4" t="inlineStr">
         <is>
-          <t>partnerships</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="O1" s="4" t="inlineStr">
@@ -547,69 +551,103 @@
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
-          <t>founder</t>
+          <t>founders</t>
         </is>
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>equipments</t>
+          <t>facilities</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
+          <t>authority</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>members</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>collections</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>graduates</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>undergraduates</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
           <t>score</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>city_id</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>numberOfEmployees</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>personnel</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>numberOfSubsidiaries</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>parent_organization_id</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>metadata</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <autoFilter ref="A1:Y1"/>
-  <dataValidations count="5">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <autoFilter ref="A1:AE1"/>
+  <dataValidations count="6">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>_lists!$B$2:$B$12</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
-      <formula1>_lists!$A$2:$A$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="V2:V1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="Y2:Y1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="W2:W1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="AA2:AA1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
+      <formula1>_lists!$A$2:$A$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB2:AB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>

--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -466,6 +466,9 @@
     <col width="24" customWidth="1" style="2" min="29" max="29"/>
     <col width="26" customWidth="1" style="1" min="30" max="30"/>
     <col width="18" customWidth="1" style="1" min="31" max="31"/>
+    <col width="18" customWidth="1" style="1" min="32" max="32"/>
+    <col width="18" customWidth="1" style="1" min="33" max="33"/>
+    <col width="23" customWidth="1" style="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -622,6 +625,21 @@
       <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>metadata</t>
+        </is>
+      </c>
+      <c r="AF1" s="4" t="inlineStr">
+        <is>
+          <t>countries</t>
+        </is>
+      </c>
+      <c r="AG1" s="4" t="inlineStr">
+        <is>
+          <t>industries</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t>working_area_cities</t>
         </is>
       </c>
     </row>
@@ -630,7 +648,7 @@
   <autoFilter ref="A1:AE1"/>
   <dataValidations count="6">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
-      <formula1>_lists!$B$2:$B$12</formula1>
+      <formula1>_lists!$B$2:$B$32</formula1>
     </dataValidation>
     <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
@@ -662,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +798,146 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
+          <t>ASSOCIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CENTRAL_BANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHAMBER_OF_COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CITY_GOVERNMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>COURT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EMBASSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FOUNDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HOSPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIBRARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MUSEUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NATIONAL_AUDIT_OFFICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NATIONAL_PARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OMBUDSMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRIMARY_SCHOOLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PUBLIC_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PUBLIC_PARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SECONDARY_SCHOOLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SOE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>STATE_GOVERNMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>THINK_TANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
           <t>OTHER</t>
         </is>
       </c>

--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -630,7 +630,7 @@
   <autoFilter ref="A1:AE1"/>
   <dataValidations count="6">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
-      <formula1>_lists!$B$2:$B$12</formula1>
+      <formula1>_lists!$B$2:$B$32</formula1>
     </dataValidation>
     <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,146 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
+          <t>ASSOCIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CENTRAL_BANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHAMBER_OF_COMMERCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CITY_GOVERNMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>COURT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EMBASSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FOUNDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HOSPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIBRARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MUSEUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NATIONAL_AUDIT_OFFICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NATIONAL_PARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OMBUDSMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRIMARY_SCHOOLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PUBLIC_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PUBLIC_PARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SECONDARY_SCHOOLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SOE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>STATE_GOVERNMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>THINK_TANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
           <t>OTHER</t>
         </is>
       </c>

--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -644,7 +644,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:AE1"/>
   <dataValidations count="6">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="2" state="veryHidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$AE$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$AJ$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -455,20 +455,22 @@
     <col width="18" customWidth="1" style="1" min="18" max="18"/>
     <col width="18" customWidth="1" style="1" min="19" max="19"/>
     <col width="18" customWidth="1" style="1" min="20" max="20"/>
-    <col width="18" customWidth="1" style="2" min="21" max="21"/>
+    <col width="18" customWidth="1" style="1" min="21" max="21"/>
     <col width="18" customWidth="1" style="1" min="22" max="22"/>
-    <col width="18" customWidth="1" style="1" min="23" max="23"/>
+    <col width="18" customWidth="1" style="2" min="23" max="23"/>
     <col width="18" customWidth="1" style="1" min="24" max="24"/>
-    <col width="18" customWidth="1" style="2" min="25" max="25"/>
+    <col width="18" customWidth="1" style="1" min="25" max="25"/>
     <col width="18" customWidth="1" style="1" min="26" max="26"/>
-    <col width="21" customWidth="1" style="1" min="27" max="27"/>
-    <col width="18" customWidth="1" style="2" min="28" max="28"/>
-    <col width="24" customWidth="1" style="2" min="29" max="29"/>
-    <col width="26" customWidth="1" style="1" min="30" max="30"/>
+    <col width="18" customWidth="1" style="2" min="27" max="27"/>
+    <col width="18" customWidth="1" style="1" min="28" max="28"/>
+    <col width="21" customWidth="1" style="1" min="29" max="29"/>
+    <col width="18" customWidth="1" style="2" min="30" max="30"/>
     <col width="18" customWidth="1" style="1" min="31" max="31"/>
-    <col width="18" customWidth="1" style="1" min="32" max="32"/>
+    <col width="26" customWidth="1" style="1" min="32" max="32"/>
     <col width="18" customWidth="1" style="1" min="33" max="33"/>
-    <col width="23" customWidth="1" style="1" min="34" max="34"/>
+    <col width="18" customWidth="1" style="1" min="34" max="34"/>
+    <col width="18" customWidth="1" style="1" min="35" max="35"/>
+    <col width="23" customWidth="1" style="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,115 +531,125 @@
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>products</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>services</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>partners</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>budget</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>founded</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>founders</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>facilities</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>offices</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>authority</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>jurisdiction</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>members</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>collections</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>graduates</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>undergraduates</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>city_id</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>numberOfEmployees</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>personnel</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
-        <is>
-          <t>numberOfSubsidiaries</t>
-        </is>
-      </c>
-      <c r="AD1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
+        <is>
+          <t>subsidiaries</t>
+        </is>
+      </c>
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>parent_organization_id</t>
         </is>
       </c>
-      <c r="AE1" s="4" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>metadata</t>
         </is>
       </c>
-      <c r="AF1" s="4" t="inlineStr">
+      <c r="AH1" s="4" t="inlineStr">
         <is>
           <t>countries</t>
         </is>
       </c>
-      <c r="AG1" s="4" t="inlineStr">
+      <c r="AI1" s="4" t="inlineStr">
         <is>
           <t>industries</t>
         </is>
       </c>
-      <c r="AH1" s="4" t="inlineStr">
+      <c r="AJ1" s="4" t="inlineStr">
         <is>
           <t>working_area_cities</t>
         </is>
@@ -645,27 +657,23 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
-  <autoFilter ref="A1:AE1"/>
-  <dataValidations count="6">
+  <autoFilter ref="A1:AJ1"/>
+  <dataValidations count="5">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>_lists!$B$2:$B$32</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="W2:W1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="Y2:Y1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="AA2:AA1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="AA2:AA1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
+    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>_lists!$A$2:$A$7</formula1>
     </dataValidation>
-    <dataValidation sqref="AB2:AB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
-      <formula1>-2147483648</formula1>
-      <formula2>2147483647</formula2>
-    </dataValidation>
-    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="AD2:AD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>

--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="2" state="veryHidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$AJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'organizations'!$A$1:$AK$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -443,8 +443,8 @@
     <col width="18" customWidth="1" style="1" min="6" max="6"/>
     <col width="18" customWidth="1" style="1" min="7" max="7"/>
     <col width="18" customWidth="1" style="1" min="8" max="8"/>
-    <col width="23" customWidth="1" style="1" min="9" max="9"/>
-    <col width="18" customWidth="1" style="1" min="10" max="10"/>
+    <col width="18" customWidth="1" style="1" min="9" max="9"/>
+    <col width="23" customWidth="1" style="1" min="10" max="10"/>
     <col width="18" customWidth="1" style="1" min="11" max="11"/>
     <col width="18" customWidth="1" style="1" min="12" max="12"/>
     <col width="18" customWidth="1" style="1" min="13" max="13"/>
@@ -457,20 +457,21 @@
     <col width="18" customWidth="1" style="1" min="20" max="20"/>
     <col width="18" customWidth="1" style="1" min="21" max="21"/>
     <col width="18" customWidth="1" style="1" min="22" max="22"/>
-    <col width="18" customWidth="1" style="2" min="23" max="23"/>
-    <col width="18" customWidth="1" style="1" min="24" max="24"/>
+    <col width="18" customWidth="1" style="1" min="23" max="23"/>
+    <col width="18" customWidth="1" style="2" min="24" max="24"/>
     <col width="18" customWidth="1" style="1" min="25" max="25"/>
     <col width="18" customWidth="1" style="1" min="26" max="26"/>
-    <col width="18" customWidth="1" style="2" min="27" max="27"/>
-    <col width="18" customWidth="1" style="1" min="28" max="28"/>
-    <col width="21" customWidth="1" style="1" min="29" max="29"/>
-    <col width="18" customWidth="1" style="2" min="30" max="30"/>
-    <col width="18" customWidth="1" style="1" min="31" max="31"/>
-    <col width="26" customWidth="1" style="1" min="32" max="32"/>
-    <col width="18" customWidth="1" style="1" min="33" max="33"/>
+    <col width="18" customWidth="1" style="1" min="27" max="27"/>
+    <col width="18" customWidth="1" style="2" min="28" max="28"/>
+    <col width="18" customWidth="1" style="1" min="29" max="29"/>
+    <col width="21" customWidth="1" style="1" min="30" max="30"/>
+    <col width="18" customWidth="1" style="2" min="31" max="31"/>
+    <col width="18" customWidth="1" style="1" min="32" max="32"/>
+    <col width="26" customWidth="1" style="1" min="33" max="33"/>
     <col width="18" customWidth="1" style="1" min="34" max="34"/>
     <col width="18" customWidth="1" style="1" min="35" max="35"/>
-    <col width="23" customWidth="1" style="1" min="36" max="36"/>
+    <col width="18" customWidth="1" style="1" min="36" max="36"/>
+    <col width="23" customWidth="1" style="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,175 +482,180 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>serial_number</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>slug</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>subtype</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>type1</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>type2</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>ownership</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>mission</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>known_for</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>programs_activities</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>research_areas</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>products</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>services</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>partners</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>budget</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>founded</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>founders</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>facilities</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>offices</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>authority</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>jurisdiction</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>members</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>collections</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>graduates</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>undergraduates</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>city_id</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>numberOfEmployees</t>
         </is>
       </c>
-      <c r="AD1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>personnel</t>
         </is>
       </c>
-      <c r="AE1" s="4" t="inlineStr">
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>subsidiaries</t>
         </is>
       </c>
-      <c r="AF1" s="4" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>parent_organization_id</t>
         </is>
       </c>
-      <c r="AG1" s="4" t="inlineStr">
+      <c r="AH1" s="4" t="inlineStr">
         <is>
           <t>metadata</t>
         </is>
       </c>
-      <c r="AH1" s="4" t="inlineStr">
+      <c r="AI1" s="4" t="inlineStr">
         <is>
           <t>countries</t>
         </is>
       </c>
-      <c r="AI1" s="4" t="inlineStr">
+      <c r="AJ1" s="4" t="inlineStr">
         <is>
           <t>industries</t>
         </is>
       </c>
-      <c r="AJ1" s="4" t="inlineStr">
+      <c r="AK1" s="4" t="inlineStr">
         <is>
           <t>working_area_cities</t>
         </is>
@@ -657,23 +663,23 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
-  <autoFilter ref="A1:AJ1"/>
+  <autoFilter ref="A1:AK1"/>
   <dataValidations count="5">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>_lists!$B$2:$B$32</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="X2:X1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="AA2:AA1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="AB2:AB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
+    <dataValidation sqref="AD2:AD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>_lists!$A$2:$A$7</formula1>
     </dataValidation>
-    <dataValidation sqref="AD2:AD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
+    <dataValidation sqref="AE2:AE1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>

--- a/apps/api/data/excel_templates/organizations.xlsx
+++ b/apps/api/data/excel_templates/organizations.xlsx
@@ -677,7 +677,7 @@
       <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation sqref="AD2:AD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
-      <formula1>_lists!$A$2:$A$7</formula1>
+      <formula1>_lists!$A$2:$A$8</formula1>
     </dataValidation>
     <dataValidation sqref="AE2:AE1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>
@@ -782,6 +782,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CLASSIFIED</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>NON_PROFIT</t>
